--- a/examples/maxdiff/Karoo_MaxDiff_Config.xlsx
+++ b/examples/maxdiff/Karoo_MaxDiff_Config.xlsx
@@ -1,407 +1,424 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duncan/Dev/Turas/examples/maxdiff/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C51665-E4BA-EF4C-85A5-67FA400F55F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="15480" yWindow="760" windowWidth="22860" windowHeight="19720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="PROJECT_SETTINGS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ITEMS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SURVEY_MAPPING" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SEGMENT_SETTINGS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="OUTPUT_SETTINGS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PROJECT_SETTINGS" sheetId="1" r:id="rId1"/>
+    <sheet name="ITEMS" sheetId="2" r:id="rId2"/>
+    <sheet name="SURVEY_MAPPING" sheetId="3" r:id="rId3"/>
+    <sheet name="SEGMENT_SETTINGS" sheetId="4" r:id="rId4"/>
+    <sheet name="OUTPUT_SETTINGS" sheetId="5" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
-  <si>
-    <t xml:space="preserve">Setting_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karoo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANALYSIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raw_Data_File</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karoo_MaxDiff_Data.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design_File</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karoo_MaxDiff_Design.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Output_Folder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_File_Sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Respondent_ID_Variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RespID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight_Variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Choice_Value_Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITEM_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand_Colour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#0d8a8a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accent_Colour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#c0392b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyst_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turas example</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research_House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Research LampPost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item_Label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item_Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anchor_Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display_Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRESH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roasted within the last two weeks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORIGIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single-origin beans with the farm named</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A lower price per kilogram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELIVERY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free delivery on every order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUBSCRIBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A subscription I can pause or change online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRIND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ground to my brewing method at no extra cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETHICAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fair pay for growers, independently verified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DECAF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A decaf that tastes like the real thing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STORE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A shop I can visit and taste before buying</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REWARDS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loyalty rewards on repeat orders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field_Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task_Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERSION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEST_CHOICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T1_Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WORST_CHOICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T1_Worst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T2_Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T2_Worst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T3_Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T3_Worst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T4_Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T4_Worst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T5_Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T5_Worst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T6_Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T6_Worst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T7_Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T7_Worst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T8_Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T8_Worst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segment_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segment_Label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segment_Def</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include_in_Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age_Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer segment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Count_Scores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Aggregate_Logit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_HB_Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Segment_Tables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Charts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_HTML_Report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Simulator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Stats_Pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_Tabs_Export</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabs_Question_Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDSHARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allow_Approx_Utilities_Export</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate_TURF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TURF_Max_Items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TURF_Threshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABOVE_MEAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Has_Anchor_Question</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anchor_Variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MustHave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anchor_Threshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anchor_Format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMMA_SEPARATED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score_Rescale_Method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0_100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Export_Individual_Utils</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min_Respondents_Per_Segment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="125">
+  <si>
+    <t>Setting_Name</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Project_Name</t>
+  </si>
+  <si>
+    <t>Karoo</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>ANALYSIS</t>
+  </si>
+  <si>
+    <t>Raw_Data_File</t>
+  </si>
+  <si>
+    <t>Karoo_MaxDiff_Data.xlsx</t>
+  </si>
+  <si>
+    <t>Design_File</t>
+  </si>
+  <si>
+    <t>Karoo_MaxDiff_Design.xlsx</t>
+  </si>
+  <si>
+    <t>Output_Folder</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>Data_File_Sheet</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Respondent_ID_Variable</t>
+  </si>
+  <si>
+    <t>RespID</t>
+  </si>
+  <si>
+    <t>Weight_Variable</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Choice_Value_Type</t>
+  </si>
+  <si>
+    <t>ITEM_ID</t>
+  </si>
+  <si>
+    <t>Seed</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>Brand_Colour</t>
+  </si>
+  <si>
+    <t>#0d8a8a</t>
+  </si>
+  <si>
+    <t>Accent_Colour</t>
+  </si>
+  <si>
+    <t>#c0392b</t>
+  </si>
+  <si>
+    <t>Analyst_Name</t>
+  </si>
+  <si>
+    <t>Turas example</t>
+  </si>
+  <si>
+    <t>Research_House</t>
+  </si>
+  <si>
+    <t>The Research LampPost</t>
+  </si>
+  <si>
+    <t>Item_ID</t>
+  </si>
+  <si>
+    <t>Item_Label</t>
+  </si>
+  <si>
+    <t>Item_Group</t>
+  </si>
+  <si>
+    <t>Include</t>
+  </si>
+  <si>
+    <t>Anchor_Item</t>
+  </si>
+  <si>
+    <t>Display_Order</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>FRESH</t>
+  </si>
+  <si>
+    <t>Roasted within the last two weeks</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>ORIGIN</t>
+  </si>
+  <si>
+    <t>Single-origin beans with the farm named</t>
+  </si>
+  <si>
+    <t>PRICE</t>
+  </si>
+  <si>
+    <t>A lower price per kilogram</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>DELIVERY</t>
+  </si>
+  <si>
+    <t>Free delivery on every order</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>SUBSCRIBE</t>
+  </si>
+  <si>
+    <t>A subscription I can pause or change online</t>
+  </si>
+  <si>
+    <t>GRIND</t>
+  </si>
+  <si>
+    <t>Ground to my brewing method at no extra cost</t>
+  </si>
+  <si>
+    <t>ETHICAL</t>
+  </si>
+  <si>
+    <t>Fair pay for growers, independently verified</t>
+  </si>
+  <si>
+    <t>Values</t>
+  </si>
+  <si>
+    <t>DECAF</t>
+  </si>
+  <si>
+    <t>A decaf that tastes like the real thing</t>
+  </si>
+  <si>
+    <t>STORE</t>
+  </si>
+  <si>
+    <t>A shop I can visit and taste before buying</t>
+  </si>
+  <si>
+    <t>REWARDS</t>
+  </si>
+  <si>
+    <t>Loyalty rewards on repeat orders</t>
+  </si>
+  <si>
+    <t>Field_Type</t>
+  </si>
+  <si>
+    <t>Field_Name</t>
+  </si>
+  <si>
+    <t>Task_Number</t>
+  </si>
+  <si>
+    <t>VERSION</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>BEST_CHOICE</t>
+  </si>
+  <si>
+    <t>T1_Best</t>
+  </si>
+  <si>
+    <t>WORST_CHOICE</t>
+  </si>
+  <si>
+    <t>T1_Worst</t>
+  </si>
+  <si>
+    <t>T2_Best</t>
+  </si>
+  <si>
+    <t>T2_Worst</t>
+  </si>
+  <si>
+    <t>T3_Best</t>
+  </si>
+  <si>
+    <t>T3_Worst</t>
+  </si>
+  <si>
+    <t>T4_Best</t>
+  </si>
+  <si>
+    <t>T4_Worst</t>
+  </si>
+  <si>
+    <t>T5_Best</t>
+  </si>
+  <si>
+    <t>T5_Worst</t>
+  </si>
+  <si>
+    <t>T6_Best</t>
+  </si>
+  <si>
+    <t>T6_Worst</t>
+  </si>
+  <si>
+    <t>T7_Best</t>
+  </si>
+  <si>
+    <t>T7_Worst</t>
+  </si>
+  <si>
+    <t>T8_Best</t>
+  </si>
+  <si>
+    <t>T8_Worst</t>
+  </si>
+  <si>
+    <t>Segment_ID</t>
+  </si>
+  <si>
+    <t>Segment_Label</t>
+  </si>
+  <si>
+    <t>Variable_Name</t>
+  </si>
+  <si>
+    <t>Segment_Def</t>
+  </si>
+  <si>
+    <t>Include_in_Output</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Age_Group</t>
+  </si>
+  <si>
+    <t>Age group</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>Customer segment</t>
+  </si>
+  <si>
+    <t>Generate_Count_Scores</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Generate_Aggregate_Logit</t>
+  </si>
+  <si>
+    <t>Generate_HB_Model</t>
+  </si>
+  <si>
+    <t>Generate_Segment_Tables</t>
+  </si>
+  <si>
+    <t>Generate_Charts</t>
+  </si>
+  <si>
+    <t>Generate_HTML_Report</t>
+  </si>
+  <si>
+    <t>Generate_Simulator</t>
+  </si>
+  <si>
+    <t>Generate_Stats_Pack</t>
+  </si>
+  <si>
+    <t>Generate_Tabs_Export</t>
+  </si>
+  <si>
+    <t>Tabs_Question_Code</t>
+  </si>
+  <si>
+    <t>MDSHARE</t>
+  </si>
+  <si>
+    <t>Allow_Approx_Utilities_Export</t>
+  </si>
+  <si>
+    <t>Generate_TURF</t>
+  </si>
+  <si>
+    <t>TURF_Max_Items</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>TURF_Threshold</t>
+  </si>
+  <si>
+    <t>ABOVE_MEAN</t>
+  </si>
+  <si>
+    <t>Has_Anchor_Question</t>
+  </si>
+  <si>
+    <t>Anchor_Variable</t>
+  </si>
+  <si>
+    <t>MustHave</t>
+  </si>
+  <si>
+    <t>Anchor_Threshold</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>Anchor_Format</t>
+  </si>
+  <si>
+    <t>COMMA_SEPARATED</t>
+  </si>
+  <si>
+    <t>Score_Rescale_Method</t>
+  </si>
+  <si>
+    <t>0_100</t>
+  </si>
+  <si>
+    <t>Export_Individual_Utils</t>
+  </si>
+  <si>
+    <t>Min_Respondents_Per_Segment</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -437,6 +454,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -718,15 +744,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -734,7 +760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -742,7 +768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -750,7 +776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -758,7 +784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -766,7 +792,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -774,7 +800,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -782,7 +808,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -790,7 +816,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -798,7 +824,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -806,7 +832,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -814,7 +840,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -822,7 +848,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -830,7 +856,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -838,7 +864,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -848,16 +874,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -880,7 +906,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -890,20 +916,20 @@
       <c r="C2" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -913,20 +939,20 @@
       <c r="C3" t="s">
         <v>39</v>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>2</v>
       </c>
       <c r="G3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -936,20 +962,20 @@
       <c r="C4" t="s">
         <v>44</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>3</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -959,20 +985,20 @@
       <c r="C5" t="s">
         <v>47</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>4</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>48</v>
       </c>
@@ -982,20 +1008,20 @@
       <c r="C6" t="s">
         <v>47</v>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>5</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -1005,20 +1031,20 @@
       <c r="C7" t="s">
         <v>39</v>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>6</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -1028,20 +1054,20 @@
       <c r="C8" t="s">
         <v>54</v>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>7</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -1051,20 +1077,20 @@
       <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>8</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -1074,20 +1100,20 @@
       <c r="C10" t="s">
         <v>47</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>9</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -1097,13 +1123,13 @@
       <c r="C11" t="s">
         <v>44</v>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>10</v>
       </c>
       <c r="G11" t="s">
@@ -1112,16 +1138,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>61</v>
       </c>
@@ -1132,203 +1158,202 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>64</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
-      <c r="C2"/>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>66</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>68</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>66</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>68</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>66</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>3</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>68</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>3</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>66</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>4</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>68</v>
       </c>
       <c r="B10" t="s">
         <v>75</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>4</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>66</v>
       </c>
       <c r="B11" t="s">
         <v>76</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>68</v>
       </c>
       <c r="B12" t="s">
         <v>77</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>66</v>
       </c>
       <c r="B13" t="s">
         <v>78</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>6</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>68</v>
       </c>
       <c r="B14" t="s">
         <v>79</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>6</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>66</v>
       </c>
       <c r="B15" t="s">
         <v>80</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>7</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>68</v>
       </c>
       <c r="B16" t="s">
         <v>81</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>7</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>66</v>
       </c>
       <c r="B17" t="s">
         <v>82</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>8</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>68</v>
       </c>
       <c r="B18" t="s">
         <v>83</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>84</v>
       </c>
@@ -1345,7 +1370,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -1358,11 +1383,11 @@
       <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>90</v>
       </c>
@@ -1375,11 +1400,11 @@
       <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>91</v>
       </c>
@@ -1392,11 +1417,11 @@
       <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>93</v>
       </c>
@@ -1409,26 +1434,26 @@
       <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1436,7 +1461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>95</v>
       </c>
@@ -1444,7 +1469,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -1452,7 +1477,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -1460,7 +1485,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>99</v>
       </c>
@@ -1468,144 +1493,144 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>100</v>
       </c>
       <c r="B6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>102</v>
-      </c>
-      <c r="B7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>103</v>
       </c>
       <c r="B8" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" t="s">
         <v>106</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>107</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>108</v>
       </c>
       <c r="B12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" t="s">
         <v>110</v>
       </c>
-      <c r="B14" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>112</v>
       </c>
-      <c r="B15" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>114</v>
       </c>
       <c r="B16" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" t="s">
         <v>115</v>
       </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>117</v>
       </c>
-      <c r="B18" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>119</v>
       </c>
-      <c r="B19" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>121</v>
       </c>
-      <c r="B20" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>122</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>123</v>
       </c>
       <c r="B21" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" t="s">
         <v>124</v>
-      </c>
-      <c r="B22" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>